--- a/data/trans_bre/P1413-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1413-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,78</t>
+          <t>1,11</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 7,78</t>
+          <t>-3,26; 7,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,61; 22,48</t>
+          <t>9,97; 22,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,09; 15,84</t>
+          <t>3,77; 16,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 6,05</t>
+          <t>-3,25; 5,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-27,01; 81,23</t>
+          <t>-22,84; 85,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>128,87; 585,6</t>
+          <t>122,56; 536,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,61; 219,61</t>
+          <t>30,12; 223,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-21,96; 86,66</t>
+          <t>-24,04; 62,94</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,35</t>
+          <t>14,48</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>103,5%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,96; 17,21</t>
+          <t>5,87; 16,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 10,44</t>
+          <t>3,01; 10,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 5,57</t>
+          <t>-0,7; 5,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,63; 20,37</t>
+          <t>9,12; 19,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,32; 92,08</t>
+          <t>23,32; 89,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,0; 262,56</t>
+          <t>34,3; 261,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 157,03</t>
+          <t>-13,65; 170,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>51,66; 170,7</t>
+          <t>48,91; 155,46</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,1</t>
+          <t>9,09</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>46,72%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 10,73</t>
+          <t>1,18; 10,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 12,26</t>
+          <t>2,61; 12,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 12,24</t>
+          <t>2,5; 12,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 14,57</t>
+          <t>3,96; 14,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,76; 182,24</t>
+          <t>9,6; 174,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,63; 221,08</t>
+          <t>21,06; 249,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,97; 225,6</t>
+          <t>24,1; 221,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,4; 87,06</t>
+          <t>17,31; 90,83</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,66</t>
+          <t>15,93</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>115,28%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,46; -0,45</t>
+          <t>-10,46; -0,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,04; 16,51</t>
+          <t>5,82; 16,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,18; 15,13</t>
+          <t>5,11; 15,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 16,82</t>
+          <t>9,93; 21,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,47; -0,54</t>
+          <t>-48,45; -0,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,44; 214,11</t>
+          <t>46,16; 220,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,03; 251,3</t>
+          <t>48,78; 245,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 124,74</t>
+          <t>55,05; 197,34</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,22</t>
+          <t>7,21</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>47,6%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 14,45</t>
+          <t>3,28; 14,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,52; 24,89</t>
+          <t>9,16; 25,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 11,04</t>
+          <t>-1,54; 10,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 12,47</t>
+          <t>1,98; 12,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,58; 402,03</t>
+          <t>27,02; 395,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,65; 224,17</t>
+          <t>43,07; 232,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 187,39</t>
+          <t>-15,78; 167,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,1; 105,27</t>
+          <t>10,47; 111,96</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10,18</t>
+          <t>10,63</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>41,59%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 7,51</t>
+          <t>-4,22; 7,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 10,2</t>
+          <t>-2,95; 9,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 8,15</t>
+          <t>-3,01; 8,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,73; 16,5</t>
+          <t>4,26; 16,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-27,63; 71,82</t>
+          <t>-25,71; 71,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 94,56</t>
+          <t>-19,32; 86,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-26,19; 135,62</t>
+          <t>-25,78; 126,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,18; 74,88</t>
+          <t>14,67; 75,32</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30,8</t>
+          <t>17,52</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>117,37%</t>
+          <t>66,91%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 2,65</t>
+          <t>-5,2; 2,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,89; 13,86</t>
+          <t>5,61; 13,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,2; 10,4</t>
+          <t>3,0; 10,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,6; 53,19</t>
+          <t>12,39; 22,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-27,92; 19,8</t>
+          <t>-30,65; 19,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,9; 156,93</t>
+          <t>43,98; 160,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,31; 134,77</t>
+          <t>26,0; 136,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>57,0; 223,97</t>
+          <t>41,85; 96,22</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15,42</t>
+          <t>10,56</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>115,71%</t>
+          <t>60,18%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 7,61</t>
+          <t>-1,62; 7,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,91; 10,0</t>
+          <t>3,6; 10,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,69; 7,11</t>
+          <t>0,84; 7,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,25; 24,74</t>
+          <t>6,46; 14,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 40,93</t>
+          <t>-7,42; 38,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,85; 142,5</t>
+          <t>36,14; 144,41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,38; 99,45</t>
+          <t>7,99; 106,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>49,23; 393,41</t>
+          <t>33,77; 90,56</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16,3</t>
+          <t>12,05</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>64,94%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,84</t>
+          <t>1,32; 4,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,52; 10,88</t>
+          <t>7,64; 10,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,42</t>
+          <t>4,21; 7,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11,26; 27,92</t>
+          <t>10,2; 13,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,7; 32,62</t>
+          <t>7,52; 31,02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>78,62; 132,41</t>
+          <t>78,34; 131,06</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46,84; 97,17</t>
+          <t>48,57; 98,7</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>58,23; 169,73</t>
+          <t>52,31; 80,04</t>
         </is>
       </c>
     </row>
